--- a/output/yearly_population_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_72_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7150</v>
+        <v>6632</v>
       </c>
       <c r="C2" t="n">
-        <v>7794</v>
+        <v>5708</v>
       </c>
       <c r="D2" t="n">
-        <v>28275</v>
+        <v>29011</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5057</v>
+        <v>3730</v>
       </c>
       <c r="C3" t="n">
-        <v>6564</v>
+        <v>5109</v>
       </c>
       <c r="D3" t="n">
-        <v>17266</v>
+        <v>16594</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3644</v>
+        <v>2651</v>
       </c>
       <c r="C4" t="n">
-        <v>5525</v>
+        <v>4664</v>
       </c>
       <c r="D4" t="n">
-        <v>8636</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2143</v>
+        <v>1854</v>
       </c>
       <c r="C5" t="n">
-        <v>4812</v>
+        <v>4024</v>
       </c>
       <c r="D5" t="n">
-        <v>3136</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1142</v>
+        <v>1066</v>
       </c>
       <c r="C6" t="n">
-        <v>3202</v>
+        <v>2452</v>
       </c>
       <c r="D6" t="n">
-        <v>1223</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>536</v>
+        <v>498</v>
       </c>
       <c r="C7" t="n">
-        <v>1982</v>
+        <v>1434</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>945</v>
+        <v>722</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
         <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8546</v>
+        <v>8052</v>
       </c>
       <c r="C2" t="n">
-        <v>8205</v>
+        <v>4373</v>
       </c>
       <c r="D2" t="n">
-        <v>25288</v>
+        <v>33880</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4873</v>
+        <v>4092</v>
       </c>
       <c r="C3" t="n">
-        <v>6269</v>
+        <v>4732</v>
       </c>
       <c r="D3" t="n">
-        <v>17542</v>
+        <v>17167</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3648</v>
+        <v>2699</v>
       </c>
       <c r="C4" t="n">
-        <v>5888</v>
+        <v>4740</v>
       </c>
       <c r="D4" t="n">
-        <v>9616</v>
+        <v>8389</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2427</v>
+        <v>1953</v>
       </c>
       <c r="C5" t="n">
-        <v>4980</v>
+        <v>4247</v>
       </c>
       <c r="D5" t="n">
-        <v>3885</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1407</v>
+        <v>1286</v>
       </c>
       <c r="C6" t="n">
-        <v>3867</v>
+        <v>3127</v>
       </c>
       <c r="D6" t="n">
-        <v>1470</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>674</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D7" t="n">
         <v>701</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2475</v>
-      </c>
-      <c r="D7" t="n">
-        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C8" t="n">
-        <v>1362</v>
+        <v>1028</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>608</v>
+        <v>505</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9581</v>
+        <v>8220</v>
       </c>
       <c r="C2" t="n">
-        <v>10379</v>
+        <v>10464</v>
       </c>
       <c r="D2" t="n">
-        <v>26524</v>
+        <v>30566</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5118</v>
+        <v>4638</v>
       </c>
       <c r="C3" t="n">
-        <v>6252</v>
+        <v>4051</v>
       </c>
       <c r="D3" t="n">
-        <v>17348</v>
+        <v>18180</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3514</v>
+        <v>2785</v>
       </c>
       <c r="C4" t="n">
-        <v>5866</v>
+        <v>4592</v>
       </c>
       <c r="D4" t="n">
-        <v>10465</v>
+        <v>9482</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2567</v>
+        <v>2010</v>
       </c>
       <c r="C5" t="n">
-        <v>5194</v>
+        <v>4376</v>
       </c>
       <c r="D5" t="n">
-        <v>4499</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1633</v>
+        <v>1440</v>
       </c>
       <c r="C6" t="n">
-        <v>4271</v>
+        <v>3540</v>
       </c>
       <c r="D6" t="n">
-        <v>1775</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>869</v>
+        <v>826</v>
       </c>
       <c r="C7" t="n">
-        <v>2981</v>
+        <v>2417</v>
       </c>
       <c r="D7" t="n">
-        <v>813</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C8" t="n">
-        <v>1762</v>
+        <v>1368</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C9" t="n">
-        <v>875</v>
+        <v>709</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>393</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
+        <v>211</v>
+      </c>
+      <c r="D11" t="n">
         <v>210</v>
-      </c>
-      <c r="D11" t="n">
-        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8852</v>
+        <v>7534</v>
       </c>
       <c r="C2" t="n">
-        <v>7223</v>
+        <v>7031</v>
       </c>
       <c r="D2" t="n">
-        <v>22051</v>
+        <v>24906</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6177</v>
+        <v>5376</v>
       </c>
       <c r="C3" t="n">
-        <v>9615</v>
+        <v>7035</v>
       </c>
       <c r="D3" t="n">
-        <v>19036</v>
+        <v>19821</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2371</v>
+        <v>1857</v>
       </c>
       <c r="C4" t="n">
-        <v>8083</v>
+        <v>6801</v>
       </c>
       <c r="D4" t="n">
-        <v>9941</v>
+        <v>8866</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1508</v>
+        <v>1330</v>
       </c>
       <c r="C5" t="n">
-        <v>4185</v>
+        <v>3469</v>
       </c>
       <c r="D5" t="n">
-        <v>2948</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>802</v>
+        <v>763</v>
       </c>
       <c r="C6" t="n">
-        <v>2921</v>
+        <v>2368</v>
       </c>
       <c r="D6" t="n">
-        <v>796</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="C7" t="n">
-        <v>1726</v>
+        <v>1340</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>857</v>
+        <v>694</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
+        <v>206</v>
+      </c>
+      <c r="D10" t="n">
         <v>205</v>
-      </c>
-      <c r="D10" t="n">
-        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5559</v>
+        <v>4585</v>
       </c>
       <c r="C2" t="n">
-        <v>3773</v>
+        <v>3596</v>
       </c>
       <c r="D2" t="n">
-        <v>15668</v>
+        <v>17533</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6287</v>
+        <v>5448</v>
       </c>
       <c r="C3" t="n">
-        <v>7781</v>
+        <v>6357</v>
       </c>
       <c r="D3" t="n">
-        <v>18532</v>
+        <v>19370</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3271</v>
+        <v>2773</v>
       </c>
       <c r="C4" t="n">
-        <v>8916</v>
+        <v>7033</v>
       </c>
       <c r="D4" t="n">
-        <v>11043</v>
+        <v>10449</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1711</v>
+        <v>1468</v>
       </c>
       <c r="C5" t="n">
-        <v>5792</v>
+        <v>4970</v>
       </c>
       <c r="D5" t="n">
-        <v>3816</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>909</v>
       </c>
       <c r="C6" t="n">
-        <v>3524</v>
+        <v>2879</v>
       </c>
       <c r="D6" t="n">
-        <v>995</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>2165</v>
+        <v>1749</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>909</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="D9" t="n">
         <v>257</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5439</v>
+        <v>4688</v>
       </c>
       <c r="C2" t="n">
-        <v>5910</v>
+        <v>5821</v>
       </c>
       <c r="D2" t="n">
-        <v>14307</v>
+        <v>16699</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5037</v>
+        <v>4259</v>
       </c>
       <c r="C3" t="n">
-        <v>5244</v>
+        <v>4392</v>
       </c>
       <c r="D3" t="n">
-        <v>16897</v>
+        <v>17772</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3870</v>
+        <v>3413</v>
       </c>
       <c r="C4" t="n">
-        <v>8185</v>
+        <v>6610</v>
       </c>
       <c r="D4" t="n">
-        <v>11929</v>
+        <v>11672</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2086</v>
+        <v>1799</v>
       </c>
       <c r="C5" t="n">
-        <v>7166</v>
+        <v>5856</v>
       </c>
       <c r="D5" t="n">
-        <v>4810</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1157</v>
+        <v>1056</v>
       </c>
       <c r="C6" t="n">
-        <v>4470</v>
+        <v>3841</v>
       </c>
       <c r="D6" t="n">
-        <v>1388</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C7" t="n">
-        <v>2758</v>
+        <v>2246</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>1544</v>
+        <v>1280</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3277</v>
+        <v>2764</v>
       </c>
       <c r="C2" t="n">
-        <v>2841</v>
+        <v>2631</v>
       </c>
       <c r="D2" t="n">
-        <v>9981</v>
+        <v>11519</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4994</v>
+        <v>4209</v>
       </c>
       <c r="C3" t="n">
-        <v>5311</v>
+        <v>4747</v>
       </c>
       <c r="D3" t="n">
-        <v>16249</v>
+        <v>17225</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4216</v>
+        <v>3768</v>
       </c>
       <c r="C4" t="n">
-        <v>7868</v>
+        <v>6403</v>
       </c>
       <c r="D4" t="n">
-        <v>12614</v>
+        <v>12463</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2132</v>
+        <v>1883</v>
       </c>
       <c r="C5" t="n">
-        <v>8560</v>
+        <v>6838</v>
       </c>
       <c r="D5" t="n">
-        <v>5064</v>
+        <v>4776</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="C6" t="n">
-        <v>5268</v>
+        <v>4689</v>
       </c>
       <c r="D6" t="n">
-        <v>1350</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>2843</v>
+        <v>2359</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1119</v>
+        <v>998</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3951</v>
+        <v>4084</v>
       </c>
       <c r="C2" t="n">
-        <v>7166</v>
+        <v>3058</v>
       </c>
       <c r="D2" t="n">
-        <v>8364</v>
+        <v>16509</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3686</v>
+        <v>3080</v>
       </c>
       <c r="C3" t="n">
-        <v>3764</v>
+        <v>3327</v>
       </c>
       <c r="D3" t="n">
-        <v>14460</v>
+        <v>15291</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3951</v>
+        <v>3456</v>
       </c>
       <c r="C4" t="n">
-        <v>6601</v>
+        <v>5520</v>
       </c>
       <c r="D4" t="n">
-        <v>12788</v>
+        <v>12861</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2616</v>
+        <v>2353</v>
       </c>
       <c r="C5" t="n">
-        <v>8083</v>
+        <v>6560</v>
       </c>
       <c r="D5" t="n">
-        <v>5997</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1238</v>
+        <v>1174</v>
       </c>
       <c r="C6" t="n">
-        <v>6682</v>
+        <v>5619</v>
       </c>
       <c r="D6" t="n">
-        <v>1844</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C7" t="n">
-        <v>3796</v>
+        <v>3363</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1748</v>
+        <v>1523</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2839</v>
+        <v>2858</v>
       </c>
       <c r="C2" t="n">
-        <v>3452</v>
+        <v>1947</v>
       </c>
       <c r="D2" t="n">
-        <v>7257</v>
+        <v>12045</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3304</v>
+        <v>2986</v>
       </c>
       <c r="C3" t="n">
-        <v>4654</v>
+        <v>2913</v>
       </c>
       <c r="D3" t="n">
-        <v>13080</v>
+        <v>14605</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3536</v>
+        <v>3051</v>
       </c>
       <c r="C4" t="n">
-        <v>5537</v>
+        <v>4637</v>
       </c>
       <c r="D4" t="n">
-        <v>12730</v>
+        <v>12920</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2867</v>
+        <v>2576</v>
       </c>
       <c r="C5" t="n">
-        <v>7635</v>
+        <v>6286</v>
       </c>
       <c r="D5" t="n">
-        <v>6646</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1461</v>
+        <v>1389</v>
       </c>
       <c r="C6" t="n">
-        <v>7382</v>
+        <v>6153</v>
       </c>
       <c r="D6" t="n">
-        <v>2177</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>4733</v>
+        <v>4167</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2235</v>
+        <v>1978</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4339</v>
+        <v>4156</v>
       </c>
       <c r="C2" t="n">
-        <v>5088</v>
+        <v>7634</v>
       </c>
       <c r="D2" t="n">
-        <v>15437</v>
+        <v>19385</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2647</v>
+        <v>2471</v>
       </c>
       <c r="C3" t="n">
-        <v>3761</v>
+        <v>2226</v>
       </c>
       <c r="D3" t="n">
-        <v>11544</v>
+        <v>13459</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3003</v>
+        <v>2630</v>
       </c>
       <c r="C4" t="n">
-        <v>5057</v>
+        <v>3779</v>
       </c>
       <c r="D4" t="n">
-        <v>12393</v>
+        <v>12645</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2848</v>
+        <v>2528</v>
       </c>
       <c r="C5" t="n">
-        <v>6650</v>
+        <v>5458</v>
       </c>
       <c r="D5" t="n">
-        <v>7261</v>
+        <v>7274</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1780</v>
+        <v>1672</v>
       </c>
       <c r="C6" t="n">
-        <v>7416</v>
+        <v>6212</v>
       </c>
       <c r="D6" t="n">
-        <v>2706</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="C7" t="n">
-        <v>5691</v>
+        <v>4924</v>
       </c>
       <c r="D7" t="n">
-        <v>899</v>
+        <v>914</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>3112</v>
+        <v>2770</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1130</v>
+        <v>1104</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7109</v>
+        <v>5481</v>
       </c>
       <c r="C2" t="n">
-        <v>7318</v>
+        <v>5646</v>
       </c>
       <c r="D2" t="n">
-        <v>7282</v>
+        <v>7589</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3140</v>
+        <v>2941</v>
       </c>
       <c r="C2" t="n">
-        <v>2971</v>
+        <v>4275</v>
       </c>
       <c r="D2" t="n">
-        <v>11486</v>
+        <v>14267</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3574</v>
+        <v>3310</v>
       </c>
       <c r="C3" t="n">
-        <v>4384</v>
+        <v>3712</v>
       </c>
       <c r="D3" t="n">
-        <v>12779</v>
+        <v>15011</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4165</v>
+        <v>3676</v>
       </c>
       <c r="C4" t="n">
-        <v>7286</v>
+        <v>5508</v>
       </c>
       <c r="D4" t="n">
-        <v>12807</v>
+        <v>12965</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1697</v>
+        <v>1638</v>
       </c>
       <c r="C5" t="n">
-        <v>10164</v>
+        <v>8424</v>
       </c>
       <c r="D5" t="n">
-        <v>6580</v>
+        <v>6629</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="C6" t="n">
-        <v>6958</v>
+        <v>6103</v>
       </c>
       <c r="D6" t="n">
-        <v>2065</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>3049</v>
+        <v>2714</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1107</v>
+        <v>1081</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7334</v>
+        <v>6102</v>
       </c>
       <c r="C2" t="n">
-        <v>9779</v>
+        <v>3945</v>
       </c>
       <c r="D2" t="n">
-        <v>22086</v>
+        <v>9247</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3019</v>
+        <v>2329</v>
       </c>
       <c r="C3" t="n">
-        <v>3688</v>
+        <v>2890</v>
       </c>
       <c r="D3" t="n">
-        <v>1862</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5398</v>
+        <v>5968</v>
       </c>
       <c r="C2" t="n">
-        <v>5455</v>
+        <v>4745</v>
       </c>
       <c r="D2" t="n">
-        <v>30037</v>
+        <v>20250</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4252</v>
+        <v>3461</v>
       </c>
       <c r="C3" t="n">
-        <v>6152</v>
+        <v>3010</v>
       </c>
       <c r="D3" t="n">
-        <v>5122</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1346</v>
+        <v>1045</v>
       </c>
       <c r="C4" t="n">
-        <v>2204</v>
+        <v>1763</v>
       </c>
       <c r="D4" t="n">
-        <v>1556</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6070</v>
+        <v>5553</v>
       </c>
       <c r="C2" t="n">
-        <v>4928</v>
+        <v>5672</v>
       </c>
       <c r="D2" t="n">
-        <v>28304</v>
+        <v>22202</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3963</v>
+        <v>3843</v>
       </c>
       <c r="C3" t="n">
-        <v>5011</v>
+        <v>3424</v>
       </c>
       <c r="D3" t="n">
-        <v>8739</v>
+        <v>5547</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2382</v>
+        <v>1907</v>
       </c>
       <c r="C4" t="n">
-        <v>4335</v>
+        <v>2415</v>
       </c>
       <c r="D4" t="n">
-        <v>2193</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>600</v>
+        <v>489</v>
       </c>
       <c r="C5" t="n">
-        <v>1302</v>
+        <v>1074</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6661</v>
+        <v>5121</v>
       </c>
       <c r="C2" t="n">
-        <v>9703</v>
+        <v>6860</v>
       </c>
       <c r="D2" t="n">
-        <v>32997</v>
+        <v>24595</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4057</v>
+        <v>3823</v>
       </c>
       <c r="C3" t="n">
-        <v>4333</v>
+        <v>3999</v>
       </c>
       <c r="D3" t="n">
-        <v>11097</v>
+        <v>7688</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2669</v>
+        <v>2416</v>
       </c>
       <c r="C4" t="n">
-        <v>4560</v>
+        <v>2916</v>
       </c>
       <c r="D4" t="n">
-        <v>3320</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1229</v>
+        <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>2847</v>
+        <v>1759</v>
       </c>
       <c r="D5" t="n">
-        <v>1335</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>799</v>
+        <v>688</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9199</v>
+        <v>6156</v>
       </c>
       <c r="C2" t="n">
-        <v>9769</v>
+        <v>8673</v>
       </c>
       <c r="D2" t="n">
-        <v>35100</v>
+        <v>33610</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3841</v>
+        <v>3257</v>
       </c>
       <c r="C3" t="n">
-        <v>5757</v>
+        <v>4493</v>
       </c>
       <c r="D3" t="n">
-        <v>12836</v>
+        <v>9141</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2060</v>
+        <v>1949</v>
       </c>
       <c r="C4" t="n">
-        <v>3629</v>
+        <v>2889</v>
       </c>
       <c r="D4" t="n">
-        <v>4048</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1016</v>
+        <v>886</v>
       </c>
       <c r="C5" t="n">
-        <v>2692</v>
+        <v>1720</v>
       </c>
       <c r="D5" t="n">
-        <v>1315</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>1219</v>
+        <v>834</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>273</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7443</v>
+        <v>4673</v>
       </c>
       <c r="C2" t="n">
-        <v>5929</v>
+        <v>4745</v>
       </c>
       <c r="D2" t="n">
-        <v>27984</v>
+        <v>32146</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5397</v>
+        <v>3935</v>
       </c>
       <c r="C3" t="n">
-        <v>6945</v>
+        <v>5993</v>
       </c>
       <c r="D3" t="n">
-        <v>15631</v>
+        <v>12760</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2579</v>
+        <v>2295</v>
       </c>
       <c r="C4" t="n">
-        <v>4820</v>
+        <v>3814</v>
       </c>
       <c r="D4" t="n">
-        <v>5696</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1365</v>
+        <v>1272</v>
       </c>
       <c r="C5" t="n">
-        <v>3175</v>
+        <v>2363</v>
       </c>
       <c r="D5" t="n">
-        <v>1787</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>625</v>
+        <v>552</v>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>1342</v>
       </c>
       <c r="D6" t="n">
-        <v>862</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>827</v>
+        <v>622</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7253</v>
+        <v>5706</v>
       </c>
       <c r="C2" t="n">
-        <v>9610</v>
+        <v>7088</v>
       </c>
       <c r="D2" t="n">
-        <v>30212</v>
+        <v>32729</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5249</v>
+        <v>3545</v>
       </c>
       <c r="C3" t="n">
-        <v>5570</v>
+        <v>4578</v>
       </c>
       <c r="D3" t="n">
-        <v>16408</v>
+        <v>14943</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3393</v>
+        <v>2693</v>
       </c>
       <c r="C4" t="n">
-        <v>5836</v>
+        <v>4989</v>
       </c>
       <c r="D4" t="n">
-        <v>7280</v>
+        <v>5596</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1704</v>
+        <v>1561</v>
       </c>
       <c r="C5" t="n">
-        <v>3993</v>
+        <v>3121</v>
       </c>
       <c r="D5" t="n">
-        <v>2445</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>896</v>
+        <v>832</v>
       </c>
       <c r="C6" t="n">
-        <v>2598</v>
+        <v>1862</v>
       </c>
       <c r="D6" t="n">
-        <v>1001</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>323</v>
       </c>
       <c r="C7" t="n">
-        <v>1436</v>
+        <v>1009</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>553</v>
+        <v>458</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_72_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6632</v>
+        <v>9405</v>
       </c>
       <c r="C2" t="n">
-        <v>5708</v>
+        <v>9736</v>
       </c>
       <c r="D2" t="n">
-        <v>29011</v>
+        <v>15393</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3730</v>
+        <v>4626</v>
       </c>
       <c r="C3" t="n">
-        <v>5109</v>
+        <v>6015</v>
       </c>
       <c r="D3" t="n">
-        <v>16594</v>
+        <v>11393</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2651</v>
+        <v>3215</v>
       </c>
       <c r="C4" t="n">
-        <v>4664</v>
+        <v>4838</v>
       </c>
       <c r="D4" t="n">
-        <v>7130</v>
+        <v>5738</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1854</v>
+        <v>2127</v>
       </c>
       <c r="C5" t="n">
-        <v>4024</v>
+        <v>3372</v>
       </c>
       <c r="D5" t="n">
-        <v>2488</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1066</v>
+        <v>1223</v>
       </c>
       <c r="C6" t="n">
-        <v>2452</v>
+        <v>2109</v>
       </c>
       <c r="D6" t="n">
-        <v>1087</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>498</v>
+        <v>611</v>
       </c>
       <c r="C7" t="n">
-        <v>1434</v>
+        <v>1372</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="C8" t="n">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8052</v>
+        <v>10490</v>
       </c>
       <c r="C2" t="n">
-        <v>4373</v>
+        <v>9525</v>
       </c>
       <c r="D2" t="n">
-        <v>33880</v>
+        <v>26060</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4092</v>
+        <v>5557</v>
       </c>
       <c r="C3" t="n">
-        <v>4732</v>
+        <v>6821</v>
       </c>
       <c r="D3" t="n">
-        <v>17167</v>
+        <v>11185</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2699</v>
+        <v>3283</v>
       </c>
       <c r="C4" t="n">
-        <v>4740</v>
+        <v>5278</v>
       </c>
       <c r="D4" t="n">
-        <v>8389</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1953</v>
+        <v>2310</v>
       </c>
       <c r="C5" t="n">
-        <v>4247</v>
+        <v>4019</v>
       </c>
       <c r="D5" t="n">
-        <v>3169</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1286</v>
+        <v>1495</v>
       </c>
       <c r="C6" t="n">
-        <v>3127</v>
+        <v>2681</v>
       </c>
       <c r="D6" t="n">
-        <v>1276</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>674</v>
+        <v>790</v>
       </c>
       <c r="C7" t="n">
-        <v>1902</v>
+        <v>1697</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>279</v>
+        <v>352</v>
       </c>
       <c r="C8" t="n">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="C9" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8220</v>
+        <v>13501</v>
       </c>
       <c r="C2" t="n">
-        <v>10464</v>
+        <v>13163</v>
       </c>
       <c r="D2" t="n">
-        <v>30566</v>
+        <v>24198</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4638</v>
+        <v>6197</v>
       </c>
       <c r="C3" t="n">
-        <v>4051</v>
+        <v>7062</v>
       </c>
       <c r="D3" t="n">
-        <v>18180</v>
+        <v>12355</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2785</v>
+        <v>3628</v>
       </c>
       <c r="C4" t="n">
-        <v>4592</v>
+        <v>5879</v>
       </c>
       <c r="D4" t="n">
-        <v>9482</v>
+        <v>6991</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2010</v>
+        <v>2407</v>
       </c>
       <c r="C5" t="n">
-        <v>4376</v>
+        <v>4452</v>
       </c>
       <c r="D5" t="n">
-        <v>3793</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1440</v>
+        <v>1673</v>
       </c>
       <c r="C6" t="n">
-        <v>3540</v>
+        <v>3233</v>
       </c>
       <c r="D6" t="n">
-        <v>1531</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>826</v>
+        <v>971</v>
       </c>
       <c r="C7" t="n">
-        <v>2417</v>
+        <v>2094</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>384</v>
+        <v>473</v>
       </c>
       <c r="C8" t="n">
-        <v>1368</v>
+        <v>1297</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="C9" t="n">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="D9" t="n">
         <v>338</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7534</v>
+        <v>12081</v>
       </c>
       <c r="C2" t="n">
-        <v>7031</v>
+        <v>8740</v>
       </c>
       <c r="D2" t="n">
-        <v>24906</v>
+        <v>19639</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5376</v>
+        <v>7103</v>
       </c>
       <c r="C3" t="n">
-        <v>7035</v>
+        <v>10883</v>
       </c>
       <c r="D3" t="n">
-        <v>19821</v>
+        <v>13660</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1857</v>
+        <v>2224</v>
       </c>
       <c r="C4" t="n">
-        <v>6801</v>
+        <v>7603</v>
       </c>
       <c r="D4" t="n">
-        <v>8866</v>
+        <v>6809</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1330</v>
+        <v>1545</v>
       </c>
       <c r="C5" t="n">
-        <v>3469</v>
+        <v>3168</v>
       </c>
       <c r="D5" t="n">
-        <v>2556</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>897</v>
       </c>
       <c r="C6" t="n">
-        <v>2368</v>
+        <v>2052</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>1340</v>
+        <v>1271</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="D8" t="n">
         <v>331</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>81</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>39</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4585</v>
+        <v>6853</v>
       </c>
       <c r="C2" t="n">
-        <v>3596</v>
+        <v>3582</v>
       </c>
       <c r="D2" t="n">
-        <v>17533</v>
+        <v>14509</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5448</v>
+        <v>7932</v>
       </c>
       <c r="C3" t="n">
-        <v>6357</v>
+        <v>8929</v>
       </c>
       <c r="D3" t="n">
-        <v>19370</v>
+        <v>13843</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2773</v>
+        <v>3580</v>
       </c>
       <c r="C4" t="n">
-        <v>7033</v>
+        <v>9311</v>
       </c>
       <c r="D4" t="n">
-        <v>10449</v>
+        <v>7719</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1468</v>
+        <v>1706</v>
       </c>
       <c r="C5" t="n">
-        <v>4970</v>
+        <v>5097</v>
       </c>
       <c r="D5" t="n">
-        <v>3314</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>909</v>
+        <v>1083</v>
       </c>
       <c r="C6" t="n">
-        <v>2879</v>
+        <v>2583</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>414</v>
       </c>
       <c r="C7" t="n">
-        <v>1749</v>
+        <v>1604</v>
       </c>
       <c r="D7" t="n">
         <v>514</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>909</v>
+        <v>884</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>38</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4688</v>
+        <v>6486</v>
       </c>
       <c r="C2" t="n">
-        <v>5821</v>
+        <v>6840</v>
       </c>
       <c r="D2" t="n">
-        <v>16699</v>
+        <v>19645</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4259</v>
+        <v>6264</v>
       </c>
       <c r="C3" t="n">
-        <v>4392</v>
+        <v>5547</v>
       </c>
       <c r="D3" t="n">
-        <v>17772</v>
+        <v>12986</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3413</v>
+        <v>4736</v>
       </c>
       <c r="C4" t="n">
-        <v>6610</v>
+        <v>9012</v>
       </c>
       <c r="D4" t="n">
-        <v>11672</v>
+        <v>8542</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1799</v>
+        <v>2213</v>
       </c>
       <c r="C5" t="n">
-        <v>5856</v>
+        <v>7013</v>
       </c>
       <c r="D5" t="n">
-        <v>4377</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1056</v>
+        <v>1243</v>
       </c>
       <c r="C6" t="n">
-        <v>3841</v>
+        <v>3740</v>
       </c>
       <c r="D6" t="n">
-        <v>1287</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>502</v>
+        <v>608</v>
       </c>
       <c r="C7" t="n">
-        <v>2246</v>
+        <v>2035</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="C8" t="n">
-        <v>1280</v>
+        <v>1195</v>
       </c>
       <c r="D8" t="n">
         <v>368</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
         <v>134</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2764</v>
+        <v>3841</v>
       </c>
       <c r="C2" t="n">
-        <v>2631</v>
+        <v>3137</v>
       </c>
       <c r="D2" t="n">
-        <v>11519</v>
+        <v>13566</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4209</v>
+        <v>6093</v>
       </c>
       <c r="C3" t="n">
-        <v>4747</v>
+        <v>5814</v>
       </c>
       <c r="D3" t="n">
-        <v>17225</v>
+        <v>13420</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3768</v>
+        <v>5224</v>
       </c>
       <c r="C4" t="n">
-        <v>6403</v>
+        <v>8525</v>
       </c>
       <c r="D4" t="n">
-        <v>12463</v>
+        <v>9118</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1883</v>
+        <v>2287</v>
       </c>
       <c r="C5" t="n">
-        <v>6838</v>
+        <v>8397</v>
       </c>
       <c r="D5" t="n">
-        <v>4776</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>902</v>
+        <v>1078</v>
       </c>
       <c r="C6" t="n">
-        <v>4689</v>
+        <v>4608</v>
       </c>
       <c r="D6" t="n">
-        <v>1269</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>2359</v>
+        <v>2172</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>998</v>
+        <v>965</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
         <v>131</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>36</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4084</v>
+        <v>4552</v>
       </c>
       <c r="C2" t="n">
-        <v>3058</v>
+        <v>6057</v>
       </c>
       <c r="D2" t="n">
-        <v>16509</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3080</v>
+        <v>4405</v>
       </c>
       <c r="C3" t="n">
-        <v>3327</v>
+        <v>4070</v>
       </c>
       <c r="D3" t="n">
-        <v>15291</v>
+        <v>12538</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3456</v>
+        <v>4925</v>
       </c>
       <c r="C4" t="n">
-        <v>5520</v>
+        <v>7046</v>
       </c>
       <c r="D4" t="n">
-        <v>12861</v>
+        <v>9542</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2353</v>
+        <v>3039</v>
       </c>
       <c r="C5" t="n">
-        <v>6560</v>
+        <v>8361</v>
       </c>
       <c r="D5" t="n">
-        <v>5811</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1174</v>
+        <v>1393</v>
       </c>
       <c r="C6" t="n">
-        <v>5619</v>
+        <v>6291</v>
       </c>
       <c r="D6" t="n">
-        <v>1769</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>420</v>
       </c>
       <c r="C7" t="n">
-        <v>3363</v>
+        <v>3171</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>1523</v>
+        <v>1433</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
         <v>176</v>
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2858</v>
+        <v>3671</v>
       </c>
       <c r="C2" t="n">
-        <v>1947</v>
+        <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>12045</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2986</v>
+        <v>3900</v>
       </c>
       <c r="C3" t="n">
-        <v>2913</v>
+        <v>4456</v>
       </c>
       <c r="D3" t="n">
-        <v>14605</v>
+        <v>11672</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3051</v>
+        <v>4394</v>
       </c>
       <c r="C4" t="n">
-        <v>4637</v>
+        <v>5873</v>
       </c>
       <c r="D4" t="n">
-        <v>12920</v>
+        <v>9746</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2576</v>
+        <v>3408</v>
       </c>
       <c r="C5" t="n">
-        <v>6286</v>
+        <v>7948</v>
       </c>
       <c r="D5" t="n">
-        <v>6558</v>
+        <v>5087</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1389</v>
+        <v>1666</v>
       </c>
       <c r="C6" t="n">
-        <v>6153</v>
+        <v>7272</v>
       </c>
       <c r="D6" t="n">
-        <v>2131</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="C7" t="n">
-        <v>4167</v>
+        <v>4120</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1978</v>
+        <v>1882</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>640</v>
+        <v>609</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4156</v>
+        <v>5853</v>
       </c>
       <c r="C2" t="n">
-        <v>7634</v>
+        <v>9088</v>
       </c>
       <c r="D2" t="n">
-        <v>19385</v>
+        <v>11751</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2471</v>
+        <v>3213</v>
       </c>
       <c r="C3" t="n">
-        <v>2226</v>
+        <v>3573</v>
       </c>
       <c r="D3" t="n">
-        <v>13459</v>
+        <v>10560</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2630</v>
+        <v>3667</v>
       </c>
       <c r="C4" t="n">
-        <v>3779</v>
+        <v>5138</v>
       </c>
       <c r="D4" t="n">
-        <v>12645</v>
+        <v>9727</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2528</v>
+        <v>3414</v>
       </c>
       <c r="C5" t="n">
-        <v>5458</v>
+        <v>6926</v>
       </c>
       <c r="D5" t="n">
-        <v>7274</v>
+        <v>5509</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1672</v>
+        <v>2100</v>
       </c>
       <c r="C6" t="n">
-        <v>6212</v>
+        <v>7475</v>
       </c>
       <c r="D6" t="n">
-        <v>2698</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>602</v>
+        <v>716</v>
       </c>
       <c r="C7" t="n">
-        <v>4924</v>
+        <v>5363</v>
       </c>
       <c r="D7" t="n">
-        <v>914</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>2770</v>
+        <v>2670</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>1104</v>
+        <v>1038</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5481</v>
+        <v>8472</v>
       </c>
       <c r="C2" t="n">
-        <v>5646</v>
+        <v>5490</v>
       </c>
       <c r="D2" t="n">
-        <v>7589</v>
+        <v>6658</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2941</v>
+        <v>4191</v>
       </c>
       <c r="C2" t="n">
-        <v>4275</v>
+        <v>5162</v>
       </c>
       <c r="D2" t="n">
-        <v>14267</v>
+        <v>8648</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3310</v>
+        <v>4408</v>
       </c>
       <c r="C3" t="n">
-        <v>3712</v>
+        <v>5161</v>
       </c>
       <c r="D3" t="n">
-        <v>15011</v>
+        <v>11543</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3676</v>
+        <v>5028</v>
       </c>
       <c r="C4" t="n">
-        <v>5508</v>
+        <v>7437</v>
       </c>
       <c r="D4" t="n">
-        <v>12965</v>
+        <v>9953</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1638</v>
+        <v>2035</v>
       </c>
       <c r="C5" t="n">
-        <v>8424</v>
+        <v>10381</v>
       </c>
       <c r="D5" t="n">
-        <v>6629</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>556</v>
+        <v>661</v>
       </c>
       <c r="C6" t="n">
-        <v>6103</v>
+        <v>6720</v>
       </c>
       <c r="D6" t="n">
-        <v>2092</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>2714</v>
+        <v>2616</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1081</v>
+        <v>1017</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6102</v>
+        <v>7281</v>
       </c>
       <c r="C2" t="n">
-        <v>3945</v>
+        <v>5059</v>
       </c>
       <c r="D2" t="n">
-        <v>9247</v>
+        <v>12357</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2329</v>
+        <v>3597</v>
       </c>
       <c r="C3" t="n">
-        <v>2890</v>
+        <v>2766</v>
       </c>
       <c r="D3" t="n">
-        <v>1914</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5968</v>
+        <v>5010</v>
       </c>
       <c r="C2" t="n">
-        <v>4745</v>
+        <v>3296</v>
       </c>
       <c r="D2" t="n">
-        <v>20250</v>
+        <v>10909</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3461</v>
+        <v>4472</v>
       </c>
       <c r="C3" t="n">
-        <v>3010</v>
+        <v>3504</v>
       </c>
       <c r="D3" t="n">
-        <v>3005</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1045</v>
+        <v>1596</v>
       </c>
       <c r="C4" t="n">
-        <v>1763</v>
+        <v>1663</v>
       </c>
       <c r="D4" t="n">
-        <v>1567</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5553</v>
+        <v>5378</v>
       </c>
       <c r="C2" t="n">
-        <v>5672</v>
+        <v>4507</v>
       </c>
       <c r="D2" t="n">
-        <v>22202</v>
+        <v>13570</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3843</v>
+        <v>3907</v>
       </c>
       <c r="C3" t="n">
-        <v>3424</v>
+        <v>2934</v>
       </c>
       <c r="D3" t="n">
-        <v>5547</v>
+        <v>4362</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1907</v>
+        <v>2574</v>
       </c>
       <c r="C4" t="n">
-        <v>2415</v>
+        <v>2671</v>
       </c>
       <c r="D4" t="n">
-        <v>1795</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>489</v>
+        <v>715</v>
       </c>
       <c r="C5" t="n">
-        <v>1074</v>
+        <v>1002</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
         <v>303</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
@@ -5294,7 +5294,7 @@
         <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5121</v>
+        <v>6837</v>
       </c>
       <c r="C2" t="n">
-        <v>6860</v>
+        <v>4286</v>
       </c>
       <c r="D2" t="n">
-        <v>24595</v>
+        <v>25762</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3823</v>
+        <v>3786</v>
       </c>
       <c r="C3" t="n">
-        <v>3999</v>
+        <v>3266</v>
       </c>
       <c r="D3" t="n">
-        <v>7688</v>
+        <v>5454</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2416</v>
+        <v>2748</v>
       </c>
       <c r="C4" t="n">
-        <v>2916</v>
+        <v>2759</v>
       </c>
       <c r="D4" t="n">
-        <v>2407</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>1378</v>
       </c>
       <c r="C5" t="n">
-        <v>1759</v>
+        <v>1862</v>
       </c>
       <c r="D5" t="n">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>688</v>
+        <v>652</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>284</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>218</v>
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6156</v>
+        <v>6953</v>
       </c>
       <c r="C2" t="n">
-        <v>8673</v>
+        <v>8347</v>
       </c>
       <c r="D2" t="n">
-        <v>33610</v>
+        <v>25482</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3257</v>
+        <v>3848</v>
       </c>
       <c r="C3" t="n">
-        <v>4493</v>
+        <v>3108</v>
       </c>
       <c r="D3" t="n">
-        <v>9141</v>
+        <v>7672</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1949</v>
+        <v>2042</v>
       </c>
       <c r="C4" t="n">
-        <v>2889</v>
+        <v>2496</v>
       </c>
       <c r="D4" t="n">
-        <v>2857</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>886</v>
+        <v>1083</v>
       </c>
       <c r="C5" t="n">
-        <v>1720</v>
+        <v>1693</v>
       </c>
       <c r="D5" t="n">
-        <v>1171</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="6">
@@ -5812,10 +5812,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="C6" t="n">
-        <v>834</v>
+        <v>858</v>
       </c>
       <c r="D6" t="n">
         <v>757</v>
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
         <v>520</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
         <v>273</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4673</v>
+        <v>6360</v>
       </c>
       <c r="C2" t="n">
-        <v>4745</v>
+        <v>7091</v>
       </c>
       <c r="D2" t="n">
-        <v>32146</v>
+        <v>22020</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3935</v>
+        <v>4511</v>
       </c>
       <c r="C3" t="n">
-        <v>5993</v>
+        <v>5384</v>
       </c>
       <c r="D3" t="n">
-        <v>12760</v>
+        <v>10229</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2295</v>
+        <v>2605</v>
       </c>
       <c r="C4" t="n">
-        <v>3814</v>
+        <v>2825</v>
       </c>
       <c r="D4" t="n">
-        <v>4097</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1272</v>
+        <v>1395</v>
       </c>
       <c r="C5" t="n">
-        <v>2363</v>
+        <v>2143</v>
       </c>
       <c r="D5" t="n">
-        <v>1475</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>552</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="D6" t="n">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="C7" t="n">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D7" t="n">
         <v>561</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>154</v>
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6241,7 +6241,7 @@
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5706</v>
+        <v>6927</v>
       </c>
       <c r="C2" t="n">
-        <v>7088</v>
+        <v>8234</v>
       </c>
       <c r="D2" t="n">
-        <v>32729</v>
+        <v>16347</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3545</v>
+        <v>4478</v>
       </c>
       <c r="C3" t="n">
-        <v>4578</v>
+        <v>5476</v>
       </c>
       <c r="D3" t="n">
-        <v>14943</v>
+        <v>11457</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2693</v>
+        <v>3092</v>
       </c>
       <c r="C4" t="n">
-        <v>4989</v>
+        <v>4264</v>
       </c>
       <c r="D4" t="n">
-        <v>5596</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1561</v>
+        <v>1770</v>
       </c>
       <c r="C5" t="n">
-        <v>3121</v>
+        <v>2484</v>
       </c>
       <c r="D5" t="n">
-        <v>1933</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>832</v>
+        <v>957</v>
       </c>
       <c r="C6" t="n">
-        <v>1862</v>
+        <v>1761</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>424</v>
       </c>
       <c r="C7" t="n">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">

--- a/output/yearly_population_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_72_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9405</v>
+        <v>1576</v>
       </c>
       <c r="C2" t="n">
-        <v>9736</v>
+        <v>4109</v>
       </c>
       <c r="D2" t="n">
-        <v>15393</v>
+        <v>12427</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4626</v>
+        <v>3032</v>
       </c>
       <c r="C3" t="n">
-        <v>6015</v>
+        <v>8568</v>
       </c>
       <c r="D3" t="n">
-        <v>11393</v>
+        <v>12942</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3215</v>
+        <v>2119</v>
       </c>
       <c r="C4" t="n">
-        <v>4838</v>
+        <v>10651</v>
       </c>
       <c r="D4" t="n">
-        <v>5738</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2127</v>
+        <v>1064</v>
       </c>
       <c r="C5" t="n">
-        <v>3372</v>
+        <v>6515</v>
       </c>
       <c r="D5" t="n">
-        <v>2199</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1223</v>
+        <v>407</v>
       </c>
       <c r="C6" t="n">
-        <v>2109</v>
+        <v>2690</v>
       </c>
       <c r="D6" t="n">
-        <v>1027</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>611</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>1372</v>
+        <v>864</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>237</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>728</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10490</v>
+        <v>1797</v>
       </c>
       <c r="C2" t="n">
-        <v>9525</v>
+        <v>10624</v>
       </c>
       <c r="D2" t="n">
-        <v>26060</v>
+        <v>12672</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5557</v>
+        <v>2013</v>
       </c>
       <c r="C3" t="n">
-        <v>6821</v>
+        <v>5591</v>
       </c>
       <c r="D3" t="n">
-        <v>11185</v>
+        <v>12076</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3283</v>
+        <v>2201</v>
       </c>
       <c r="C4" t="n">
-        <v>5278</v>
+        <v>9349</v>
       </c>
       <c r="D4" t="n">
-        <v>6540</v>
+        <v>6901</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2310</v>
+        <v>1349</v>
       </c>
       <c r="C5" t="n">
-        <v>4019</v>
+        <v>8506</v>
       </c>
       <c r="D5" t="n">
-        <v>2688</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1495</v>
+        <v>621</v>
       </c>
       <c r="C6" t="n">
-        <v>2681</v>
+        <v>4488</v>
       </c>
       <c r="D6" t="n">
-        <v>1204</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>790</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>352</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1018</v>
+        <v>574</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>13501</v>
+        <v>984</v>
       </c>
       <c r="C2" t="n">
-        <v>13163</v>
+        <v>4688</v>
       </c>
       <c r="D2" t="n">
-        <v>24198</v>
+        <v>8740</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6197</v>
+        <v>1900</v>
       </c>
       <c r="C3" t="n">
-        <v>7062</v>
+        <v>7206</v>
       </c>
       <c r="D3" t="n">
-        <v>12355</v>
+        <v>11852</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3628</v>
+        <v>2374</v>
       </c>
       <c r="C4" t="n">
-        <v>5879</v>
+        <v>8717</v>
       </c>
       <c r="D4" t="n">
-        <v>6991</v>
+        <v>7519</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2407</v>
+        <v>1331</v>
       </c>
       <c r="C5" t="n">
-        <v>4452</v>
+        <v>9888</v>
       </c>
       <c r="D5" t="n">
-        <v>3197</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1673</v>
+        <v>444</v>
       </c>
       <c r="C6" t="n">
-        <v>3233</v>
+        <v>5417</v>
       </c>
       <c r="D6" t="n">
-        <v>1390</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>971</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2094</v>
+        <v>1539</v>
       </c>
       <c r="D7" t="n">
-        <v>756</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>473</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1297</v>
+        <v>487</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>702</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>357</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12081</v>
+        <v>795</v>
       </c>
       <c r="C2" t="n">
-        <v>8740</v>
+        <v>6987</v>
       </c>
       <c r="D2" t="n">
-        <v>19639</v>
+        <v>12017</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7103</v>
+        <v>1293</v>
       </c>
       <c r="C3" t="n">
-        <v>10883</v>
+        <v>5308</v>
       </c>
       <c r="D3" t="n">
-        <v>13660</v>
+        <v>10702</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2224</v>
+        <v>1917</v>
       </c>
       <c r="C4" t="n">
-        <v>7603</v>
+        <v>7865</v>
       </c>
       <c r="D4" t="n">
-        <v>6809</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1545</v>
+        <v>1592</v>
       </c>
       <c r="C5" t="n">
-        <v>3168</v>
+        <v>9226</v>
       </c>
       <c r="D5" t="n">
-        <v>2252</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>897</v>
+        <v>697</v>
       </c>
       <c r="C6" t="n">
-        <v>2052</v>
+        <v>7445</v>
       </c>
       <c r="D6" t="n">
-        <v>740</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>1271</v>
+        <v>3149</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>687</v>
+        <v>903</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6853</v>
+        <v>586</v>
       </c>
       <c r="C2" t="n">
-        <v>3582</v>
+        <v>4276</v>
       </c>
       <c r="D2" t="n">
-        <v>14509</v>
+        <v>9989</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7932</v>
+        <v>984</v>
       </c>
       <c r="C3" t="n">
-        <v>8929</v>
+        <v>5429</v>
       </c>
       <c r="D3" t="n">
-        <v>13843</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3580</v>
+        <v>1593</v>
       </c>
       <c r="C4" t="n">
-        <v>9311</v>
+        <v>6823</v>
       </c>
       <c r="D4" t="n">
-        <v>7719</v>
+        <v>8194</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1706</v>
+        <v>1657</v>
       </c>
       <c r="C5" t="n">
-        <v>5097</v>
+        <v>8865</v>
       </c>
       <c r="D5" t="n">
-        <v>2860</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1083</v>
+        <v>848</v>
       </c>
       <c r="C6" t="n">
-        <v>2583</v>
+        <v>8337</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>414</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>1604</v>
+        <v>4500</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>884</v>
+        <v>1396</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6486</v>
+        <v>1776</v>
       </c>
       <c r="C2" t="n">
-        <v>6840</v>
+        <v>12137</v>
       </c>
       <c r="D2" t="n">
-        <v>19645</v>
+        <v>10867</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6264</v>
+        <v>702</v>
       </c>
       <c r="C3" t="n">
-        <v>5547</v>
+        <v>4422</v>
       </c>
       <c r="D3" t="n">
-        <v>12986</v>
+        <v>9643</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4736</v>
+        <v>1200</v>
       </c>
       <c r="C4" t="n">
-        <v>9012</v>
+        <v>6065</v>
       </c>
       <c r="D4" t="n">
-        <v>8542</v>
+        <v>8279</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2213</v>
+        <v>1500</v>
       </c>
       <c r="C5" t="n">
-        <v>7013</v>
+        <v>7818</v>
       </c>
       <c r="D5" t="n">
-        <v>3566</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1243</v>
+        <v>1053</v>
       </c>
       <c r="C6" t="n">
-        <v>3740</v>
+        <v>8476</v>
       </c>
       <c r="D6" t="n">
-        <v>1186</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>2035</v>
+        <v>6046</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1195</v>
+        <v>2534</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>603</v>
+        <v>731</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
+        <v>66</v>
+      </c>
+      <c r="D14" t="n">
         <v>55</v>
-      </c>
-      <c r="D14" t="n">
-        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3841</v>
+        <v>1250</v>
       </c>
       <c r="C2" t="n">
-        <v>3137</v>
+        <v>6796</v>
       </c>
       <c r="D2" t="n">
-        <v>13566</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6093</v>
+        <v>1136</v>
       </c>
       <c r="C3" t="n">
-        <v>5814</v>
+        <v>6648</v>
       </c>
       <c r="D3" t="n">
-        <v>13420</v>
+        <v>10429</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5224</v>
+        <v>1984</v>
       </c>
       <c r="C4" t="n">
-        <v>8525</v>
+        <v>8658</v>
       </c>
       <c r="D4" t="n">
-        <v>9118</v>
+        <v>8475</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2287</v>
+        <v>1028</v>
       </c>
       <c r="C5" t="n">
-        <v>8397</v>
+        <v>11740</v>
       </c>
       <c r="D5" t="n">
-        <v>3879</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1078</v>
+        <v>324</v>
       </c>
       <c r="C6" t="n">
-        <v>4608</v>
+        <v>7669</v>
       </c>
       <c r="D6" t="n">
-        <v>1167</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2172</v>
+        <v>2483</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>965</v>
+        <v>716</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" t="n">
         <v>53</v>
-      </c>
-      <c r="D13" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4552</v>
+        <v>655</v>
       </c>
       <c r="C2" t="n">
-        <v>6057</v>
+        <v>3928</v>
       </c>
       <c r="D2" t="n">
-        <v>11010</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4405</v>
+        <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>4070</v>
+        <v>5942</v>
       </c>
       <c r="D3" t="n">
-        <v>12538</v>
+        <v>9366</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4925</v>
+        <v>1346</v>
       </c>
       <c r="C4" t="n">
-        <v>7046</v>
+        <v>7280</v>
       </c>
       <c r="D4" t="n">
-        <v>9542</v>
+        <v>8180</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3039</v>
+        <v>988</v>
       </c>
       <c r="C5" t="n">
-        <v>8361</v>
+        <v>9096</v>
       </c>
       <c r="D5" t="n">
-        <v>4565</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1393</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>6291</v>
+        <v>7693</v>
       </c>
       <c r="D6" t="n">
-        <v>1553</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>3171</v>
+        <v>3246</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1433</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>524</v>
+        <v>256</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>116</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3671</v>
+        <v>1240</v>
       </c>
       <c r="C2" t="n">
-        <v>3390</v>
+        <v>7641</v>
       </c>
       <c r="D2" t="n">
-        <v>8631</v>
+        <v>11210</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3900</v>
+        <v>709</v>
       </c>
       <c r="C3" t="n">
-        <v>4456</v>
+        <v>4295</v>
       </c>
       <c r="D3" t="n">
-        <v>11672</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4394</v>
+        <v>1037</v>
       </c>
       <c r="C4" t="n">
-        <v>5873</v>
+        <v>6422</v>
       </c>
       <c r="D4" t="n">
-        <v>9746</v>
+        <v>8147</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3408</v>
+        <v>1040</v>
       </c>
       <c r="C5" t="n">
-        <v>7948</v>
+        <v>8070</v>
       </c>
       <c r="D5" t="n">
-        <v>5087</v>
+        <v>4726</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1666</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>7272</v>
+        <v>8286</v>
       </c>
       <c r="D6" t="n">
-        <v>1825</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>395</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>4120</v>
+        <v>5368</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1882</v>
+        <v>1915</v>
       </c>
       <c r="D8" t="n">
-        <v>425</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>609</v>
+        <v>503</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5853</v>
+        <v>1579</v>
       </c>
       <c r="C2" t="n">
-        <v>9088</v>
+        <v>18773</v>
       </c>
       <c r="D2" t="n">
-        <v>11751</v>
+        <v>13679</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3213</v>
+        <v>763</v>
       </c>
       <c r="C3" t="n">
-        <v>3573</v>
+        <v>5118</v>
       </c>
       <c r="D3" t="n">
-        <v>10560</v>
+        <v>8098</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3667</v>
+        <v>777</v>
       </c>
       <c r="C4" t="n">
-        <v>5138</v>
+        <v>5267</v>
       </c>
       <c r="D4" t="n">
-        <v>9727</v>
+        <v>7916</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3414</v>
+        <v>949</v>
       </c>
       <c r="C5" t="n">
-        <v>6926</v>
+        <v>7142</v>
       </c>
       <c r="D5" t="n">
-        <v>5509</v>
+        <v>5062</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2100</v>
+        <v>693</v>
       </c>
       <c r="C6" t="n">
-        <v>7475</v>
+        <v>8111</v>
       </c>
       <c r="D6" t="n">
-        <v>2239</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="7">
@@ -3649,10 +3649,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>716</v>
+        <v>274</v>
       </c>
       <c r="C7" t="n">
-        <v>5363</v>
+        <v>6571</v>
       </c>
       <c r="D7" t="n">
         <v>856</v>
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2670</v>
+        <v>3369</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8472</v>
+        <v>9004</v>
       </c>
       <c r="C2" t="n">
-        <v>5490</v>
+        <v>15250</v>
       </c>
       <c r="D2" t="n">
-        <v>6658</v>
+        <v>12288</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4191</v>
+        <v>1158</v>
       </c>
       <c r="C2" t="n">
-        <v>5162</v>
+        <v>22619</v>
       </c>
       <c r="D2" t="n">
-        <v>8648</v>
+        <v>14602</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4408</v>
+        <v>876</v>
       </c>
       <c r="C3" t="n">
-        <v>5161</v>
+        <v>9359</v>
       </c>
       <c r="D3" t="n">
-        <v>11543</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5028</v>
+        <v>670</v>
       </c>
       <c r="C4" t="n">
-        <v>7437</v>
+        <v>5043</v>
       </c>
       <c r="D4" t="n">
-        <v>9953</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2035</v>
+        <v>810</v>
       </c>
       <c r="C5" t="n">
-        <v>10381</v>
+        <v>6219</v>
       </c>
       <c r="D5" t="n">
-        <v>5116</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>661</v>
+        <v>727</v>
       </c>
       <c r="C6" t="n">
-        <v>6720</v>
+        <v>7580</v>
       </c>
       <c r="D6" t="n">
-        <v>1826</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>386</v>
       </c>
       <c r="C7" t="n">
-        <v>2616</v>
+        <v>7172</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>1017</v>
+        <v>4527</v>
       </c>
       <c r="D8" t="n">
-        <v>305</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>1903</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>559</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>37</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7281</v>
+        <v>7307</v>
       </c>
       <c r="C2" t="n">
-        <v>5059</v>
+        <v>15654</v>
       </c>
       <c r="D2" t="n">
-        <v>12357</v>
+        <v>18515</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3597</v>
+        <v>2899</v>
       </c>
       <c r="C3" t="n">
-        <v>2766</v>
+        <v>6022</v>
       </c>
       <c r="D3" t="n">
-        <v>1757</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5010</v>
+        <v>4430</v>
       </c>
       <c r="C2" t="n">
-        <v>3296</v>
+        <v>7087</v>
       </c>
       <c r="D2" t="n">
-        <v>10909</v>
+        <v>20512</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4472</v>
+        <v>4259</v>
       </c>
       <c r="C3" t="n">
-        <v>3504</v>
+        <v>10096</v>
       </c>
       <c r="D3" t="n">
-        <v>3408</v>
+        <v>4974</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1596</v>
+        <v>1338</v>
       </c>
       <c r="C4" t="n">
-        <v>1663</v>
+        <v>3748</v>
       </c>
       <c r="D4" t="n">
-        <v>1535</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5378</v>
+        <v>3947</v>
       </c>
       <c r="C2" t="n">
-        <v>4507</v>
+        <v>6745</v>
       </c>
       <c r="D2" t="n">
-        <v>13570</v>
+        <v>25670</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3907</v>
+        <v>3585</v>
       </c>
       <c r="C3" t="n">
-        <v>2934</v>
+        <v>7238</v>
       </c>
       <c r="D3" t="n">
-        <v>4362</v>
+        <v>7218</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2574</v>
+        <v>2432</v>
       </c>
       <c r="C4" t="n">
-        <v>2671</v>
+        <v>7387</v>
       </c>
       <c r="D4" t="n">
-        <v>1847</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>715</v>
+        <v>607</v>
       </c>
       <c r="C5" t="n">
-        <v>1002</v>
+        <v>2209</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6837</v>
+        <v>3891</v>
       </c>
       <c r="C2" t="n">
-        <v>4286</v>
+        <v>8616</v>
       </c>
       <c r="D2" t="n">
-        <v>25762</v>
+        <v>24840</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3786</v>
+        <v>3103</v>
       </c>
       <c r="C3" t="n">
-        <v>3266</v>
+        <v>6063</v>
       </c>
       <c r="D3" t="n">
-        <v>5454</v>
+        <v>9514</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2748</v>
+        <v>2585</v>
       </c>
       <c r="C4" t="n">
-        <v>2759</v>
+        <v>7151</v>
       </c>
       <c r="D4" t="n">
-        <v>2231</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1378</v>
+        <v>1267</v>
       </c>
       <c r="C5" t="n">
-        <v>1862</v>
+        <v>4875</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>368</v>
+        <v>305</v>
       </c>
       <c r="C6" t="n">
-        <v>652</v>
+        <v>1269</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6953</v>
+        <v>3397</v>
       </c>
       <c r="C2" t="n">
-        <v>8347</v>
+        <v>12308</v>
       </c>
       <c r="D2" t="n">
-        <v>25482</v>
+        <v>25802</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3848</v>
+        <v>2881</v>
       </c>
       <c r="C3" t="n">
-        <v>3108</v>
+        <v>6388</v>
       </c>
       <c r="D3" t="n">
-        <v>7672</v>
+        <v>11066</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2042</v>
+        <v>2418</v>
       </c>
       <c r="C4" t="n">
-        <v>2496</v>
+        <v>6380</v>
       </c>
       <c r="D4" t="n">
-        <v>2380</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1083</v>
+        <v>1637</v>
       </c>
       <c r="C5" t="n">
-        <v>1693</v>
+        <v>5909</v>
       </c>
       <c r="D5" t="n">
-        <v>1148</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>415</v>
+        <v>649</v>
       </c>
       <c r="C6" t="n">
-        <v>858</v>
+        <v>2986</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>321</v>
+        <v>750</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6360</v>
+        <v>3356</v>
       </c>
       <c r="C2" t="n">
-        <v>7091</v>
+        <v>11064</v>
       </c>
       <c r="D2" t="n">
-        <v>22020</v>
+        <v>20422</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4511</v>
+        <v>2562</v>
       </c>
       <c r="C3" t="n">
-        <v>5384</v>
+        <v>7952</v>
       </c>
       <c r="D3" t="n">
-        <v>10229</v>
+        <v>12326</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2605</v>
+        <v>2242</v>
       </c>
       <c r="C4" t="n">
-        <v>2825</v>
+        <v>6189</v>
       </c>
       <c r="D4" t="n">
-        <v>3425</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1395</v>
+        <v>1761</v>
       </c>
       <c r="C5" t="n">
-        <v>2143</v>
+        <v>6003</v>
       </c>
       <c r="D5" t="n">
-        <v>1350</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>952</v>
       </c>
       <c r="C6" t="n">
-        <v>1336</v>
+        <v>4218</v>
       </c>
       <c r="D6" t="n">
-        <v>824</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>631</v>
+        <v>1735</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>277</v>
+        <v>490</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6927</v>
+        <v>3165</v>
       </c>
       <c r="C2" t="n">
-        <v>8234</v>
+        <v>7169</v>
       </c>
       <c r="D2" t="n">
-        <v>16347</v>
+        <v>16529</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4478</v>
+        <v>3612</v>
       </c>
       <c r="C3" t="n">
-        <v>5476</v>
+        <v>11632</v>
       </c>
       <c r="D3" t="n">
-        <v>11457</v>
+        <v>13098</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3092</v>
+        <v>1627</v>
       </c>
       <c r="C4" t="n">
-        <v>4264</v>
+        <v>9387</v>
       </c>
       <c r="D4" t="n">
-        <v>4692</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1770</v>
+        <v>879</v>
       </c>
       <c r="C5" t="n">
-        <v>2484</v>
+        <v>4133</v>
       </c>
       <c r="D5" t="n">
-        <v>1707</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>957</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>1761</v>
+        <v>1700</v>
       </c>
       <c r="D6" t="n">
-        <v>900</v>
+        <v>621</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>424</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>1004</v>
+        <v>480</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>464</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
